--- a/outputs/Bread_percentile_classification_matrix.xlsx
+++ b/outputs/Bread_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="140">
   <si>
     <t>2020 May</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>Minimal</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Alert</t>
@@ -1258,13 +1261,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1272,7 +1275,7 @@
         <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
         <v>108</v>
@@ -1290,25 +1293,25 @@
         <v>108</v>
       </c>
       <c r="H3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I3" t="s">
         <v>108</v>
       </c>
       <c r="J3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O3" t="s">
         <v>108</v>
@@ -1326,73 +1329,73 @@
         <v>108</v>
       </c>
       <c r="T3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="W3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y3" t="s">
         <v>108</v>
       </c>
       <c r="Z3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB3" t="s">
         <v>108</v>
       </c>
       <c r="AC3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AM3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AQ3" t="s">
         <v>108</v>
@@ -1404,19 +1407,19 @@
         <v>108</v>
       </c>
       <c r="AT3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU3" t="s">
         <v>108</v>
       </c>
       <c r="AV3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AX3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY3" t="s">
         <v>108</v>
@@ -1443,13 +1446,13 @@
         <v>108</v>
       </c>
       <c r="BG3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BJ3" t="s">
         <v>108</v>
@@ -1476,22 +1479,22 @@
         <v>108</v>
       </c>
       <c r="BR3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1571,16 +1574,16 @@
         <v>108</v>
       </c>
       <c r="Z4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD4" t="s">
         <v>108</v>
@@ -1712,13 +1715,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1786,73 +1789,73 @@
         <v>108</v>
       </c>
       <c r="V5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="W5" t="s">
         <v>108</v>
       </c>
       <c r="X5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AP5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AQ5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS5" t="s">
         <v>108</v>
@@ -1939,13 +1942,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2007,61 +2010,61 @@
         <v>108</v>
       </c>
       <c r="T6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM6" t="s">
         <v>108</v>
@@ -2166,13 +2169,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2270,22 +2273,22 @@
         <v>108</v>
       </c>
       <c r="AF7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AL7" t="s">
         <v>108</v>
@@ -2393,13 +2396,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2452,76 +2455,76 @@
         <v>108</v>
       </c>
       <c r="Q8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO8" t="s">
         <v>108</v>
@@ -2620,13 +2623,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2694,73 +2697,73 @@
         <v>108</v>
       </c>
       <c r="V9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="W9" t="s">
         <v>108</v>
       </c>
       <c r="X9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC9" t="s">
         <v>108</v>
       </c>
       <c r="AD9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AI9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AJ9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO9" t="s">
         <v>108</v>
       </c>
       <c r="AP9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS9" t="s">
         <v>108</v>
@@ -2847,13 +2850,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2933,31 +2936,31 @@
         <v>108</v>
       </c>
       <c r="Z10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AI10" t="s">
         <v>108</v>
@@ -2975,25 +2978,25 @@
         <v>108</v>
       </c>
       <c r="AN10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AP10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AU10" t="s">
         <v>108</v>
@@ -3074,13 +3077,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BV10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BW10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3091,7 +3094,7 @@
         <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
         <v>108</v>
@@ -3103,13 +3106,13 @@
         <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J11" t="s">
         <v>108</v>
@@ -3124,190 +3127,190 @@
         <v>108</v>
       </c>
       <c r="N11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P11" t="s">
         <v>108</v>
       </c>
       <c r="Q11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S11" t="s">
         <v>108</v>
       </c>
       <c r="T11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V11" t="s">
         <v>108</v>
       </c>
       <c r="W11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AC11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD11" t="s">
         <v>108</v>
       </c>
       <c r="AE11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AM11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT11" t="s">
         <v>108</v>
       </c>
       <c r="AU11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AX11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA11" t="s">
         <v>108</v>
       </c>
       <c r="BB11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BE11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BJ11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BK11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BL11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BM11" t="s">
         <v>108</v>
       </c>
       <c r="BN11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BO11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BQ11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BR11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT11" t="s">
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3360,7 +3363,7 @@
         <v>108</v>
       </c>
       <c r="Q12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R12" t="s">
         <v>108</v>
@@ -3384,46 +3387,46 @@
         <v>108</v>
       </c>
       <c r="Y12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z12" t="s">
         <v>108</v>
       </c>
       <c r="AA12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM12" t="s">
         <v>108</v>
@@ -3528,13 +3531,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BV12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3623,76 +3626,76 @@
         <v>108</v>
       </c>
       <c r="AC13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AD13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AL13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AM13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AP13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AU13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AV13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AX13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AY13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AZ13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BA13" t="s">
         <v>108</v>
@@ -3755,13 +3758,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BV13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3847,13 +3850,13 @@
         <v>108</v>
       </c>
       <c r="AB14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AD14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AE14" t="s">
         <v>108</v>
@@ -3883,13 +3886,13 @@
         <v>108</v>
       </c>
       <c r="AN14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AP14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ14" t="s">
         <v>108</v>
@@ -3982,13 +3985,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BW14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4014,10 +4017,10 @@
         <v>108</v>
       </c>
       <c r="H15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J15" t="s">
         <v>108</v>
@@ -4047,10 +4050,10 @@
         <v>108</v>
       </c>
       <c r="S15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U15" t="s">
         <v>108</v>
@@ -4080,16 +4083,16 @@
         <v>108</v>
       </c>
       <c r="AD15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AE15" t="s">
         <v>108</v>
       </c>
       <c r="AF15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH15" t="s">
         <v>108</v>
@@ -4116,16 +4119,16 @@
         <v>108</v>
       </c>
       <c r="AP15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR15" t="s">
         <v>108</v>
       </c>
       <c r="AS15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT15" t="s">
         <v>108</v>
@@ -4152,16 +4155,16 @@
         <v>108</v>
       </c>
       <c r="BB15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC15" t="s">
         <v>108</v>
       </c>
       <c r="BD15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BE15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF15" t="s">
         <v>108</v>
@@ -4191,10 +4194,10 @@
         <v>108</v>
       </c>
       <c r="BO15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BQ15" t="s">
         <v>108</v>
@@ -4209,13 +4212,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4223,226 +4226,226 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
         <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K16" t="s">
         <v>108</v>
       </c>
       <c r="L16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R16" t="s">
         <v>108</v>
       </c>
       <c r="S16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X16" t="s">
         <v>108</v>
       </c>
       <c r="Y16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA16" t="s">
         <v>108</v>
       </c>
       <c r="AB16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AC16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD16" t="s">
         <v>108</v>
       </c>
       <c r="AE16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ16" t="s">
         <v>108</v>
       </c>
       <c r="AK16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AM16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AX16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ16" t="s">
         <v>108</v>
       </c>
       <c r="BA16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BE16" t="s">
         <v>108</v>
       </c>
       <c r="BF16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BJ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BK16" t="s">
         <v>108</v>
       </c>
       <c r="BL16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BM16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BN16" t="s">
         <v>108</v>
       </c>
       <c r="BO16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BQ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BR16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BU16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4558,7 +4561,7 @@
         <v>108</v>
       </c>
       <c r="AL17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM17" t="s">
         <v>108</v>
@@ -4663,13 +4666,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BV17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4752,43 +4755,43 @@
         <v>108</v>
       </c>
       <c r="AA18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AB18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN18" t="s">
         <v>108</v>
@@ -4803,7 +4806,7 @@
         <v>108</v>
       </c>
       <c r="AR18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AS18" t="s">
         <v>108</v>
@@ -4890,13 +4893,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BV18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4985,55 +4988,55 @@
         <v>108</v>
       </c>
       <c r="AC19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AQ19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR19" t="s">
         <v>108</v>
       </c>
       <c r="AS19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT19" t="s">
         <v>108</v>
@@ -5042,19 +5045,19 @@
         <v>108</v>
       </c>
       <c r="AV19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AY19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AZ19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BA19" t="s">
         <v>108</v>
@@ -5117,13 +5120,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BV19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5188,31 +5191,31 @@
         <v>108</v>
       </c>
       <c r="U20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD20" t="s">
         <v>108</v>
@@ -5224,31 +5227,31 @@
         <v>108</v>
       </c>
       <c r="AG20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AL20" t="s">
         <v>108</v>
       </c>
       <c r="AM20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AP20" t="s">
         <v>108</v>
@@ -5344,13 +5347,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
+        <v>121</v>
+      </c>
+      <c r="BV20" t="s">
         <v>120</v>
       </c>
-      <c r="BV20" t="s">
-        <v>119</v>
-      </c>
       <c r="BW20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5466,13 +5469,13 @@
         <v>108</v>
       </c>
       <c r="AL21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO21" t="s">
         <v>108</v>
@@ -5484,31 +5487,31 @@
         <v>108</v>
       </c>
       <c r="AR21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AT21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AU21" t="s">
         <v>108</v>
       </c>
       <c r="AV21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW21" t="s">
         <v>108</v>
       </c>
       <c r="AX21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AY21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AZ21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BA21" t="s">
         <v>108</v>
@@ -5520,31 +5523,31 @@
         <v>108</v>
       </c>
       <c r="BD21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BE21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BF21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BG21" t="s">
         <v>108</v>
       </c>
       <c r="BH21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BI21" t="s">
         <v>108</v>
       </c>
       <c r="BJ21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BK21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BL21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BM21" t="s">
         <v>108</v>
@@ -5556,13 +5559,13 @@
         <v>108</v>
       </c>
       <c r="BP21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BS21" t="s">
         <v>108</v>
@@ -5571,13 +5574,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BV21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BW21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5798,13 +5801,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5884,28 +5887,28 @@
         <v>108</v>
       </c>
       <c r="Z23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH23" t="s">
         <v>108</v>
@@ -5932,16 +5935,16 @@
         <v>108</v>
       </c>
       <c r="AP23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT23" t="s">
         <v>108</v>
@@ -6025,13 +6028,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BV23" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW23" t="s">
         <v>125</v>
-      </c>
-      <c r="BW23" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6120,97 +6123,97 @@
         <v>108</v>
       </c>
       <c r="AC24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AD24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AE24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AI24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AJ24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AP24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AU24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AV24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AY24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AZ24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BA24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BB24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BC24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BD24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BE24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BG24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BH24" t="s">
         <v>108</v>
@@ -6219,10 +6222,10 @@
         <v>108</v>
       </c>
       <c r="BJ24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BK24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BL24" t="s">
         <v>108</v>
@@ -6252,13 +6255,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BV24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BW24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6329,49 +6332,49 @@
         <v>108</v>
       </c>
       <c r="W25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL25" t="s">
         <v>108</v>
@@ -6479,13 +6482,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6574,13 +6577,13 @@
         <v>108</v>
       </c>
       <c r="AC26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF26" t="s">
         <v>108</v>
@@ -6592,25 +6595,25 @@
         <v>108</v>
       </c>
       <c r="AI26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP26" t="s">
         <v>108</v>
@@ -6622,7 +6625,7 @@
         <v>108</v>
       </c>
       <c r="AS26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AT26" t="s">
         <v>108</v>
@@ -6637,13 +6640,13 @@
         <v>108</v>
       </c>
       <c r="AX26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AY26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AZ26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BA26" t="s">
         <v>108</v>
@@ -6658,7 +6661,7 @@
         <v>108</v>
       </c>
       <c r="BE26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BF26" t="s">
         <v>108</v>
@@ -6673,10 +6676,10 @@
         <v>108</v>
       </c>
       <c r="BJ26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BK26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BL26" t="s">
         <v>108</v>
@@ -6694,7 +6697,7 @@
         <v>108</v>
       </c>
       <c r="BQ26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BR26" t="s">
         <v>108</v>
@@ -6706,13 +6709,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BW26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6792,19 +6795,19 @@
         <v>108</v>
       </c>
       <c r="Z27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AD27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AE27" t="s">
         <v>108</v>
@@ -6834,67 +6837,67 @@
         <v>108</v>
       </c>
       <c r="AN27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AQ27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AR27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AS27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AT27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AU27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AV27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AW27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AY27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AZ27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BA27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BB27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BC27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BD27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BE27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BF27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BH27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BI27" t="s">
         <v>108</v>
@@ -6933,13 +6936,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BW27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7160,13 +7163,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7279,10 +7282,10 @@
         <v>108</v>
       </c>
       <c r="AK29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AL29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM29" t="s">
         <v>108</v>
@@ -7294,7 +7297,7 @@
         <v>108</v>
       </c>
       <c r="AP29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ29" t="s">
         <v>108</v>
@@ -7387,13 +7390,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BV29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BW29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7614,13 +7617,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7685,7 +7688,7 @@
         <v>108</v>
       </c>
       <c r="U31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="V31" t="s">
         <v>108</v>
@@ -7700,61 +7703,61 @@
         <v>108</v>
       </c>
       <c r="Z31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AI31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AJ31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK31" t="s">
         <v>108</v>
       </c>
       <c r="AL31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AM31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AQ31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS31" t="s">
         <v>108</v>
@@ -7841,13 +7844,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BV31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BW31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -8047,34 +8050,34 @@
         <v>108</v>
       </c>
       <c r="BN32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BO32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BP32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BQ32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BR32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BS32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BT32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BU32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BV32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8139,7 +8142,7 @@
         <v>108</v>
       </c>
       <c r="U33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="V33" t="s">
         <v>108</v>
@@ -8295,13 +8298,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8369,55 +8372,55 @@
         <v>108</v>
       </c>
       <c r="V34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="W34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y34" t="s">
         <v>108</v>
       </c>
       <c r="Z34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM34" t="s">
         <v>108</v>
@@ -8429,10 +8432,10 @@
         <v>108</v>
       </c>
       <c r="AP34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR34" t="s">
         <v>108</v>
@@ -8522,13 +8525,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
+        <v>125</v>
+      </c>
+      <c r="BV34" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW34" t="s">
         <v>124</v>
-      </c>
-      <c r="BV34" t="s">
-        <v>130</v>
-      </c>
-      <c r="BW34" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Bread_percentile_classification_matrix.xlsx
+++ b/outputs/Bread_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="111">
   <si>
     <t>2020 May</t>
   </si>
@@ -346,94 +346,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>27%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>32%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>18%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
-    <t>34%</t>
-  </si>
-  <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>46%</t>
-  </si>
-  <si>
-    <t>37%</t>
   </si>
 </sst>
 </file>
@@ -1261,13 +1174,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1293,7 +1206,7 @@
         <v>108</v>
       </c>
       <c r="H3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I3" t="s">
         <v>108</v>
@@ -1329,13 +1242,13 @@
         <v>108</v>
       </c>
       <c r="T3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="U3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="V3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W3" t="s">
         <v>109</v>
@@ -1344,31 +1257,31 @@
         <v>109</v>
       </c>
       <c r="Y3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z3" t="s">
         <v>109</v>
       </c>
       <c r="AA3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB3" t="s">
         <v>108</v>
       </c>
       <c r="AC3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH3" t="s">
         <v>109</v>
@@ -1386,16 +1299,16 @@
         <v>109</v>
       </c>
       <c r="AM3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AN3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AP3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AQ3" t="s">
         <v>108</v>
@@ -1410,7 +1323,7 @@
         <v>109</v>
       </c>
       <c r="AU3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV3" t="s">
         <v>109</v>
@@ -1455,7 +1368,7 @@
         <v>109</v>
       </c>
       <c r="BJ3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BK3" t="s">
         <v>108</v>
@@ -1488,13 +1401,13 @@
         <v>109</v>
       </c>
       <c r="BU3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW3" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1574,16 +1487,16 @@
         <v>108</v>
       </c>
       <c r="Z4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD4" t="s">
         <v>108</v>
@@ -1715,13 +1628,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV4" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW4" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1789,73 +1702,73 @@
         <v>108</v>
       </c>
       <c r="V5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W5" t="s">
         <v>108</v>
       </c>
       <c r="X5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AA5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AO5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AQ5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS5" t="s">
         <v>108</v>
@@ -1942,13 +1855,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV5" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BW5" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2010,61 +1923,61 @@
         <v>108</v>
       </c>
       <c r="T6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="U6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="V6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="W6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="X6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Z6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s">
         <v>108</v>
@@ -2169,13 +2082,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2273,22 +2186,22 @@
         <v>108</v>
       </c>
       <c r="AF7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL7" t="s">
         <v>108</v>
@@ -2396,13 +2309,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV7" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW7" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2455,76 +2368,76 @@
         <v>108</v>
       </c>
       <c r="Q8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="R8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="S8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="T8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="U8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="V8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="W8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="X8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Y8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Z8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AA8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AN8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO8" t="s">
         <v>108</v>
@@ -2623,13 +2536,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BV8" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW8" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2697,73 +2610,73 @@
         <v>108</v>
       </c>
       <c r="V9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W9" t="s">
         <v>108</v>
       </c>
       <c r="X9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Y9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Z9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AA9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC9" t="s">
         <v>108</v>
       </c>
       <c r="AD9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AN9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s">
         <v>108</v>
       </c>
       <c r="AP9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS9" t="s">
         <v>108</v>
@@ -2850,13 +2763,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW9" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2936,31 +2849,31 @@
         <v>108</v>
       </c>
       <c r="Z10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI10" t="s">
         <v>108</v>
@@ -2978,25 +2891,25 @@
         <v>108</v>
       </c>
       <c r="AN10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU10" t="s">
         <v>108</v>
@@ -3077,13 +2990,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BV10" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BW10" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3091,7 +3004,7 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
         <v>109</v>
@@ -3118,13 +3031,13 @@
         <v>108</v>
       </c>
       <c r="K11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s">
         <v>108</v>
       </c>
       <c r="M11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N11" t="s">
         <v>109</v>
@@ -3142,7 +3055,7 @@
         <v>109</v>
       </c>
       <c r="S11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T11" t="s">
         <v>109</v>
@@ -3304,13 +3217,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3363,7 +3276,7 @@
         <v>108</v>
       </c>
       <c r="Q12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="R12" t="s">
         <v>108</v>
@@ -3387,46 +3300,46 @@
         <v>108</v>
       </c>
       <c r="Y12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z12" t="s">
         <v>108</v>
       </c>
       <c r="AA12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM12" t="s">
         <v>108</v>
@@ -3531,13 +3444,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV12" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW12" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3626,76 +3539,76 @@
         <v>108</v>
       </c>
       <c r="AC13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AZ13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA13" t="s">
         <v>108</v>
@@ -3758,13 +3671,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BV13" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW13" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3850,13 +3763,13 @@
         <v>108</v>
       </c>
       <c r="AB14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE14" t="s">
         <v>108</v>
@@ -3886,13 +3799,13 @@
         <v>108</v>
       </c>
       <c r="AN14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ14" t="s">
         <v>108</v>
@@ -3985,13 +3898,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV14" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="BW14" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4011,7 +3924,7 @@
         <v>108</v>
       </c>
       <c r="F15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G15" t="s">
         <v>108</v>
@@ -4047,7 +3960,7 @@
         <v>108</v>
       </c>
       <c r="R15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S15" t="s">
         <v>109</v>
@@ -4125,7 +4038,7 @@
         <v>109</v>
       </c>
       <c r="AR15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS15" t="s">
         <v>109</v>
@@ -4191,7 +4104,7 @@
         <v>108</v>
       </c>
       <c r="BN15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BO15" t="s">
         <v>109</v>
@@ -4212,13 +4125,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4253,7 +4166,7 @@
         <v>109</v>
       </c>
       <c r="K16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s">
         <v>109</v>
@@ -4292,7 +4205,7 @@
         <v>109</v>
       </c>
       <c r="X16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y16" t="s">
         <v>109</v>
@@ -4328,7 +4241,7 @@
         <v>109</v>
       </c>
       <c r="AJ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK16" t="s">
         <v>109</v>
@@ -4376,7 +4289,7 @@
         <v>109</v>
       </c>
       <c r="AZ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA16" t="s">
         <v>109</v>
@@ -4391,7 +4304,7 @@
         <v>109</v>
       </c>
       <c r="BE16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF16" t="s">
         <v>109</v>
@@ -4439,13 +4352,13 @@
         <v>109</v>
       </c>
       <c r="BU16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4468,7 +4381,7 @@
         <v>108</v>
       </c>
       <c r="G17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H17" t="s">
         <v>108</v>
@@ -4504,7 +4417,7 @@
         <v>108</v>
       </c>
       <c r="S17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T17" t="s">
         <v>108</v>
@@ -4540,7 +4453,7 @@
         <v>108</v>
       </c>
       <c r="AE17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF17" t="s">
         <v>108</v>
@@ -4561,7 +4474,7 @@
         <v>108</v>
       </c>
       <c r="AL17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM17" t="s">
         <v>108</v>
@@ -4576,7 +4489,7 @@
         <v>108</v>
       </c>
       <c r="AQ17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR17" t="s">
         <v>108</v>
@@ -4612,7 +4525,7 @@
         <v>108</v>
       </c>
       <c r="BC17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD17" t="s">
         <v>108</v>
@@ -4648,7 +4561,7 @@
         <v>108</v>
       </c>
       <c r="BO17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP17" t="s">
         <v>108</v>
@@ -4666,13 +4579,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BV17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW17" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4755,43 +4668,43 @@
         <v>108</v>
       </c>
       <c r="AA18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AN18" t="s">
         <v>108</v>
@@ -4806,7 +4719,7 @@
         <v>108</v>
       </c>
       <c r="AR18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AS18" t="s">
         <v>108</v>
@@ -4893,13 +4806,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV18" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW18" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4988,55 +4901,55 @@
         <v>108</v>
       </c>
       <c r="AC19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AN19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AO19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AP19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AQ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR19" t="s">
         <v>108</v>
       </c>
       <c r="AS19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT19" t="s">
         <v>108</v>
@@ -5045,19 +4958,19 @@
         <v>108</v>
       </c>
       <c r="AV19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AX19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AY19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AZ19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BA19" t="s">
         <v>108</v>
@@ -5120,13 +5033,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="BV19" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW19" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5191,31 +5104,31 @@
         <v>108</v>
       </c>
       <c r="U20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="V20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="W20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="X20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Y20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Z20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AA20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD20" t="s">
         <v>108</v>
@@ -5227,31 +5140,31 @@
         <v>108</v>
       </c>
       <c r="AG20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL20" t="s">
         <v>108</v>
       </c>
       <c r="AM20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP20" t="s">
         <v>108</v>
@@ -5347,13 +5260,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV20" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BW20" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5469,13 +5382,13 @@
         <v>108</v>
       </c>
       <c r="AL21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AN21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AO21" t="s">
         <v>108</v>
@@ -5487,31 +5400,31 @@
         <v>108</v>
       </c>
       <c r="AR21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AT21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU21" t="s">
         <v>108</v>
       </c>
       <c r="AV21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW21" t="s">
         <v>108</v>
       </c>
       <c r="AX21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AY21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AZ21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BA21" t="s">
         <v>108</v>
@@ -5523,31 +5436,31 @@
         <v>108</v>
       </c>
       <c r="BD21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BE21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BF21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BG21" t="s">
         <v>108</v>
       </c>
       <c r="BH21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BI21" t="s">
         <v>108</v>
       </c>
       <c r="BJ21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BK21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BL21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BM21" t="s">
         <v>108</v>
@@ -5559,13 +5472,13 @@
         <v>108</v>
       </c>
       <c r="BP21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BR21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS21" t="s">
         <v>108</v>
@@ -5574,13 +5487,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BV21" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BW21" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5801,13 +5714,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5887,28 +5800,28 @@
         <v>108</v>
       </c>
       <c r="Z23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA23" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB23" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC23" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD23" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH23" t="s">
         <v>108</v>
@@ -5935,16 +5848,16 @@
         <v>108</v>
       </c>
       <c r="AP23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT23" t="s">
         <v>108</v>
@@ -6028,13 +5941,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BV23" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BW23" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6123,97 +6036,97 @@
         <v>108</v>
       </c>
       <c r="AC24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AN24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AO24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AX24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AY24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AZ24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BA24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BB24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BC24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BD24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BE24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BF24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BG24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BH24" t="s">
         <v>108</v>
@@ -6222,10 +6135,10 @@
         <v>108</v>
       </c>
       <c r="BJ24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BK24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BL24" t="s">
         <v>108</v>
@@ -6255,13 +6168,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BV24" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="BW24" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6332,49 +6245,49 @@
         <v>108</v>
       </c>
       <c r="W25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="X25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Y25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Z25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AA25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL25" t="s">
         <v>108</v>
@@ -6482,13 +6395,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW25" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6577,13 +6490,13 @@
         <v>108</v>
       </c>
       <c r="AC26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF26" t="s">
         <v>108</v>
@@ -6595,25 +6508,25 @@
         <v>108</v>
       </c>
       <c r="AI26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AN26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AO26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AP26" t="s">
         <v>108</v>
@@ -6625,7 +6538,7 @@
         <v>108</v>
       </c>
       <c r="AS26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AT26" t="s">
         <v>108</v>
@@ -6640,13 +6553,13 @@
         <v>108</v>
       </c>
       <c r="AX26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AY26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AZ26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA26" t="s">
         <v>108</v>
@@ -6661,7 +6574,7 @@
         <v>108</v>
       </c>
       <c r="BE26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BF26" t="s">
         <v>108</v>
@@ -6676,10 +6589,10 @@
         <v>108</v>
       </c>
       <c r="BJ26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BK26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BL26" t="s">
         <v>108</v>
@@ -6697,7 +6610,7 @@
         <v>108</v>
       </c>
       <c r="BQ26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR26" t="s">
         <v>108</v>
@@ -6709,13 +6622,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BV26" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BW26" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6795,19 +6708,19 @@
         <v>108</v>
       </c>
       <c r="Z27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE27" t="s">
         <v>108</v>
@@ -6837,67 +6750,67 @@
         <v>108</v>
       </c>
       <c r="AN27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AP27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AQ27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AR27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AS27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AT27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AU27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AV27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AW27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AX27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AY27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AZ27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BA27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BB27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BC27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BD27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BE27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BF27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BG27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BH27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BI27" t="s">
         <v>108</v>
@@ -6936,13 +6849,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BV27" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BW27" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7163,13 +7076,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7282,10 +7195,10 @@
         <v>108</v>
       </c>
       <c r="AK29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL29" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM29" t="s">
         <v>108</v>
@@ -7297,7 +7210,7 @@
         <v>108</v>
       </c>
       <c r="AP29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ29" t="s">
         <v>108</v>
@@ -7390,13 +7303,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BV29" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="BW29" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7617,13 +7530,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7688,7 +7601,7 @@
         <v>108</v>
       </c>
       <c r="U31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V31" t="s">
         <v>108</v>
@@ -7703,61 +7616,61 @@
         <v>108</v>
       </c>
       <c r="Z31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK31" t="s">
         <v>108</v>
       </c>
       <c r="AL31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AO31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AP31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AQ31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS31" t="s">
         <v>108</v>
@@ -7844,13 +7757,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BV31" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BW31" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -8050,34 +7963,34 @@
         <v>108</v>
       </c>
       <c r="BN32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BO32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BP32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BQ32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BR32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BS32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BT32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BV32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW32" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8142,7 +8055,7 @@
         <v>108</v>
       </c>
       <c r="U33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V33" t="s">
         <v>108</v>
@@ -8298,13 +8211,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV33" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW33" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8372,55 +8285,55 @@
         <v>108</v>
       </c>
       <c r="V34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y34" t="s">
         <v>108</v>
       </c>
       <c r="Z34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AG34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AJ34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM34" t="s">
         <v>108</v>
@@ -8432,10 +8345,10 @@
         <v>108</v>
       </c>
       <c r="AP34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR34" t="s">
         <v>108</v>
@@ -8525,13 +8438,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BV34" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="BW34" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Bread_percentile_classification_matrix.xlsx
+++ b/outputs/Bread_percentile_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
